--- a/workshop_registration_form_templates/023_peer_specialist_training_registration--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/023_peer_specialist_training_registration--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>user_info_job_type</t>
+          <t>user_info_job_type_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Job Type</t>
+          <t>User Info Job Type 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -915,12 +915,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>user_info_hours</t>
+          <t>user_info_hours_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hours Worked</t>
+          <t>User Info Hours 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -938,12 +938,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>contact_number_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Contact Number 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>training_info_training_name</t>
+          <t>training_info_training_name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Training Name</t>
+          <t>Training Info Training Name 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>training_info_start_date</t>
+          <t>training_info_start_date_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Start Date</t>
+          <t>Training Info Start Date 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>training_info_end_date</t>
+          <t>training_info_end_date_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>End Date</t>
+          <t>Training Info End Date 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>training_info_location</t>
+          <t>training_info_location_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Training Info Location 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1181,7 +1181,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>user_info_job_type_choices</t>
+          <t>user_info_job_type_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1198,7 +1198,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>user_info_job_type_choices</t>
+          <t>user_info_job_type_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>user_info_job_type_choices</t>
+          <t>user_info_job_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
